--- a/Tools/Config/Datas/__enums__.xlsx
+++ b/Tools/Config/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -2431,6 +2431,470 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CombatButton</t>
+        </is>
+      </c>
+      <c r="C86" t="b">
+        <v>0</v>
+      </c>
+      <c r="D86" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>普攻键 ButtonX</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>战技键 ButtonB</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Dodge</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>2</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>闪避键 ButtonY</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Ultimate</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>3</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>终结技键 ButtonA</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CombatPress</t>
+        </is>
+      </c>
+      <c r="C91" t="b">
+        <v>0</v>
+      </c>
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>点按；与运行时 PressType.Click 对应</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>长按；与运行时 PressType.LongPress 对应</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SkillCategory</t>
+        </is>
+      </c>
+      <c r="C94" t="b">
+        <v>0</v>
+      </c>
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>BasicAttack</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>普攻连段</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>HeavyAttack</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>蓄力</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>DashAttack</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>3</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>冲刺攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>DodgeCounter</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>4</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>闪避反击</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Dodge</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>5</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>闪避</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>6</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>战技</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ExSpecial</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>7</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>EX 战技</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Ultimate</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>8</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>终结技</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>9</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>连携</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>QuickAssist</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>10</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>快速支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>DefensiveAssist</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>11</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>防御支援/招架</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>EvasiveAssist</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>12</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>回避支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>AssistFollowUp</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>13</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>支援突击</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>CorePassive</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>14</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>核心被动</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>AdditionalAbility</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>15</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>额外能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>16</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>轴窗边分支</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>EnemyActive</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>17</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>敌人主动技</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>AdditionalCondition</t>
+        </is>
+      </c>
+      <c r="C113" t="b">
+        <v>0</v>
+      </c>
+      <c r="D113" t="b">
+        <v>1</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>无条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>SameAttribute</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>同属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>SameFaction</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>2</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>同阵营</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>AttributeOrFaction</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>3</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>同属性或同阵营</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Tools/Config/Datas/__enums__.xlsx
+++ b/Tools/Config/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -2432,464 +2432,472 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="0" t="inlineStr">
         <is>
           <t>CombatButton</t>
         </is>
       </c>
-      <c r="C86" t="b">
+      <c r="C86" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D86" t="b">
-        <v>1</v>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="D86" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" s="0" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="J86" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K86" s="0" t="inlineStr">
         <is>
           <t>普攻键 ButtonX</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="H87" t="inlineStr">
+      <c r="H87" s="0" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="inlineStr">
+      <c r="J87" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="0" t="inlineStr">
         <is>
           <t>战技键 ButtonB</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="H88" t="inlineStr">
+      <c r="H88" s="0" t="inlineStr">
         <is>
           <t>Dodge</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="J88" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K88" s="0" t="inlineStr">
         <is>
           <t>闪避键 ButtonY</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="0" t="inlineStr">
         <is>
           <t>Ultimate</t>
         </is>
       </c>
-      <c r="J89" t="n">
+      <c r="J89" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K89" s="0" t="inlineStr">
         <is>
           <t>终结技键 ButtonA</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="0" t="inlineStr">
         <is>
           <t>CombatPress</t>
         </is>
       </c>
-      <c r="C91" t="b">
+      <c r="C91" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D91" t="b">
-        <v>1</v>
-      </c>
-      <c r="H91" t="inlineStr">
+      <c r="D91" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" s="0" t="inlineStr">
         <is>
           <t>Click</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="J91" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K91" s="0" t="inlineStr">
         <is>
           <t>点按；与运行时 PressType.Click 对应</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="H92" t="inlineStr">
+      <c r="H92" s="0" t="inlineStr">
         <is>
           <t>Hold</t>
         </is>
       </c>
-      <c r="J92" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" t="inlineStr">
+      <c r="J92" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" s="0" t="inlineStr">
         <is>
           <t>长按；与运行时 PressType.LongPress 对应</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="0" t="inlineStr">
         <is>
           <t>SkillCategory</t>
         </is>
       </c>
-      <c r="C94" t="b">
+      <c r="C94" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D94" t="b">
-        <v>1</v>
-      </c>
-      <c r="H94" t="inlineStr">
+      <c r="D94" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J94" t="n">
+      <c r="J94" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="K94" s="0" t="inlineStr">
         <is>
           <t>未分类</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="H95" t="inlineStr">
+      <c r="H95" s="0" t="inlineStr">
         <is>
           <t>BasicAttack</t>
         </is>
       </c>
-      <c r="J95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" t="inlineStr">
+      <c r="J95" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" s="0" t="inlineStr">
         <is>
           <t>普攻连段</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="H96" t="inlineStr">
+      <c r="H96" s="0" t="inlineStr">
         <is>
           <t>HeavyAttack</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="J96" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="K96" s="0" t="inlineStr">
         <is>
           <t>蓄力</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="H97" t="inlineStr">
+      <c r="H97" s="0" t="inlineStr">
         <is>
           <t>DashAttack</t>
         </is>
       </c>
-      <c r="J97" t="n">
+      <c r="J97" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="K97" s="0" t="inlineStr">
         <is>
           <t>冲刺攻击</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="H98" t="inlineStr">
+      <c r="H98" s="0" t="inlineStr">
         <is>
           <t>DodgeCounter</t>
         </is>
       </c>
-      <c r="J98" t="n">
+      <c r="J98" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K98" s="0" t="inlineStr">
         <is>
           <t>闪避反击</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="H99" t="inlineStr">
+      <c r="H99" s="0" t="inlineStr">
         <is>
           <t>Dodge</t>
         </is>
       </c>
-      <c r="J99" t="n">
+      <c r="J99" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K99" s="0" t="inlineStr">
         <is>
           <t>闪避</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="H100" t="inlineStr">
+      <c r="H100" s="0" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="J100" t="n">
+      <c r="J100" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K100" s="0" t="inlineStr">
         <is>
           <t>战技</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="H101" t="inlineStr">
+      <c r="H101" s="0" t="inlineStr">
         <is>
           <t>ExSpecial</t>
         </is>
       </c>
-      <c r="J101" t="n">
+      <c r="J101" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="K101" s="0" t="inlineStr">
         <is>
           <t>EX 战技</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="H102" t="inlineStr">
+      <c r="H102" s="0" t="inlineStr">
         <is>
           <t>Ultimate</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="J102" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K102" s="0" t="inlineStr">
         <is>
           <t>终结技</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="H103" t="inlineStr">
+      <c r="H103" s="0" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="J103" t="n">
+      <c r="J103" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="K103" s="0" t="inlineStr">
         <is>
           <t>连携</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="H104" t="inlineStr">
+      <c r="H104" s="0" t="inlineStr">
         <is>
           <t>QuickAssist</t>
         </is>
       </c>
-      <c r="J104" t="n">
+      <c r="J104" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K104" s="0" t="inlineStr">
         <is>
           <t>快速支援</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="H105" t="inlineStr">
+      <c r="H105" s="0" t="inlineStr">
         <is>
           <t>DefensiveAssist</t>
         </is>
       </c>
-      <c r="J105" t="n">
+      <c r="J105" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K105" s="0" t="inlineStr">
         <is>
           <t>防御支援/招架</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="H106" t="inlineStr">
+      <c r="H106" s="0" t="inlineStr">
         <is>
           <t>EvasiveAssist</t>
         </is>
       </c>
-      <c r="J106" t="n">
+      <c r="J106" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="K106" s="0" t="inlineStr">
         <is>
           <t>回避支援</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="H107" t="inlineStr">
+      <c r="H107" s="0" t="inlineStr">
         <is>
           <t>AssistFollowUp</t>
         </is>
       </c>
-      <c r="J107" t="n">
+      <c r="J107" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="K107" s="0" t="inlineStr">
         <is>
           <t>支援突击</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="H108" t="inlineStr">
+      <c r="H108" s="0" t="inlineStr">
         <is>
           <t>CorePassive</t>
         </is>
       </c>
-      <c r="J108" t="n">
+      <c r="J108" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="K108" s="0" t="inlineStr">
         <is>
           <t>核心被动</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="H109" t="inlineStr">
+      <c r="H109" s="0" t="inlineStr">
         <is>
           <t>AdditionalAbility</t>
         </is>
       </c>
-      <c r="J109" t="n">
+      <c r="J109" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="K109" s="0" t="inlineStr">
         <is>
           <t>额外能力</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="H110" t="inlineStr">
+      <c r="H110" s="0" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="J110" t="n">
+      <c r="J110" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="K110" s="0" t="inlineStr">
         <is>
           <t>轴窗边分支</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="H111" t="inlineStr">
+      <c r="H111" s="0" t="inlineStr">
         <is>
           <t>EnemyActive</t>
         </is>
       </c>
-      <c r="J111" t="n">
+      <c r="J111" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="K111" s="0" t="inlineStr">
         <is>
           <t>敌人主动技</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" t="inlineStr">
+    <row r="112">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>HarmonyBreak</t>
+        </is>
+      </c>
+    </row>
+    <row r="113"/>
+    <row r="114">
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>AdditionalCondition</t>
         </is>
       </c>
-      <c r="C113" t="b">
+      <c r="C114" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D113" t="b">
-        <v>1</v>
-      </c>
-      <c r="H113" t="inlineStr">
+      <c r="D114" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H114" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J113" t="n">
+      <c r="J114" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="K114" s="0" t="inlineStr">
         <is>
           <t>无条件</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="H114" t="inlineStr">
+    <row r="115">
+      <c r="H115" s="0" t="inlineStr">
         <is>
           <t>SameAttribute</t>
         </is>
       </c>
-      <c r="J114" t="n">
-        <v>1</v>
-      </c>
-      <c r="K114" t="inlineStr">
+      <c r="J115" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" s="0" t="inlineStr">
         <is>
           <t>同属性</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="H115" t="inlineStr">
+    <row r="116">
+      <c r="H116" s="0" t="inlineStr">
         <is>
           <t>SameFaction</t>
         </is>
       </c>
-      <c r="J115" t="n">
+      <c r="J116" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="K116" s="0" t="inlineStr">
         <is>
           <t>同阵营</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="H116" t="inlineStr">
+    <row r="117">
+      <c r="H117" s="0" t="inlineStr">
         <is>
           <t>AttributeOrFaction</t>
         </is>
       </c>
-      <c r="J116" t="n">
+      <c r="J117" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="K117" s="0" t="inlineStr">
         <is>
           <t>同属性或同阵营</t>
         </is>

--- a/Tools/Config/Datas/__enums__.xlsx
+++ b/Tools/Config/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -1314,6 +1314,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
         <is>
@@ -1382,6 +1383,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
         <is>
@@ -1483,6 +1485,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="0" t="inlineStr">
         <is>
@@ -1569,6 +1572,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
         <is>
@@ -1881,6 +1885,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="B49" s="0" t="inlineStr">
         <is>
@@ -1952,6 +1957,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="B54" s="0" t="inlineStr">
         <is>
@@ -2304,6 +2310,7 @@
         </is>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="B77" s="0" t="inlineStr">
         <is>
@@ -2390,6 +2397,7 @@
         </is>
       </c>
     </row>
+    <row r="82"/>
     <row r="83">
       <c r="B83" s="0" t="inlineStr">
         <is>
@@ -2431,6 +2439,7 @@
         </is>
       </c>
     </row>
+    <row r="85"/>
     <row r="86">
       <c r="B86" s="0" t="inlineStr">
         <is>
@@ -2502,6 +2511,7 @@
         </is>
       </c>
     </row>
+    <row r="90"/>
     <row r="91">
       <c r="B91" s="0" t="inlineStr">
         <is>
@@ -2543,6 +2553,7 @@
         </is>
       </c>
     </row>
+    <row r="93"/>
     <row r="94">
       <c r="B94" s="0" t="inlineStr">
         <is>
@@ -2825,7 +2836,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="H112" t="inlineStr">
+      <c r="H112" s="0" t="inlineStr">
         <is>
           <t>HarmonyBreak</t>
         </is>
@@ -2900,6 +2911,83 @@
       <c r="K117" s="0" t="inlineStr">
         <is>
           <t>同属性或同阵营</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="n"/>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>MonsterRank</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D119" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E119" s="0" t="n"/>
+      <c r="F119" s="0" t="n"/>
+      <c r="G119" s="0" t="n"/>
+      <c r="H119" s="0" t="inlineStr">
+        <is>
+          <t>Grunt</t>
+        </is>
+      </c>
+      <c r="I119" s="0" t="n"/>
+      <c r="J119" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="0" t="inlineStr">
+        <is>
+          <t>杂兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="n"/>
+      <c r="B120" s="0" t="n"/>
+      <c r="C120" s="0" t="n"/>
+      <c r="D120" s="0" t="n"/>
+      <c r="E120" s="0" t="n"/>
+      <c r="F120" s="0" t="n"/>
+      <c r="G120" s="0" t="n"/>
+      <c r="H120" s="0" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="I120" s="0" t="n"/>
+      <c r="J120" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" s="0" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="n"/>
+      <c r="B121" s="0" t="n"/>
+      <c r="C121" s="0" t="n"/>
+      <c r="D121" s="0" t="n"/>
+      <c r="E121" s="0" t="n"/>
+      <c r="F121" s="0" t="n"/>
+      <c r="G121" s="0" t="n"/>
+      <c r="H121" s="0" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="I121" s="0" t="n"/>
+      <c r="J121" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K121" s="0" t="inlineStr">
+        <is>
+          <t>首领</t>
         </is>
       </c>
     </row>
